--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -788,17 +788,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -892,22 +892,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.6</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -788,17 +788,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -840,22 +840,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -892,22 +892,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>5.6</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -944,22 +944,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -783,22 +783,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -835,27 +835,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -887,27 +887,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.8</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -939,27 +939,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -991,22 +991,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -835,27 +835,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -887,27 +887,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>7.7</t>
         </is>
       </c>
     </row>
@@ -939,27 +939,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -991,22 +991,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-12</t>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -673,7 +673,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>Para cada variable de estratificación, cuántos estudios la declaran en el texto completo, cuántos la mencionan sin poder clasificarla, cuántos callan y de cuántos no hay texto, y en cuántos el resumen no permite asignarla: separa el silencio del resumen del silencio del artículo. En «No asignable en el resumen» cuenta tanto el resumen sin valor como el que la deja como no clasificable. Lo calcula el canal (build_tabla3_completitud.py) sobre la pre-extracción desde el resumen (S4) y la extracción adjudicada (S14).</t>
         </is>
       </c>
     </row>
@@ -514,164 +521,175 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sección 3.4. Las columnas del texto completo son las de la tabla 2; la columna del resumen de esa tabla se calcula aparte, sobre S4.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas; allí la tabla 2 (completitud de las variables) es la Tabla 3.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>5 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: variable</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Nombre interno de la variable</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: campo</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>declarado_texto_completo</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Declarado en el texto completo</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: declarado_texto_completo</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>declarado_no_clasificable</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Declarado pero no clasificable</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: declarado_no_clasificable</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>no_declarado_texto_completo</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>No declarado en el texto completo</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: no_declarado_texto_completo</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>texto_no_recuperado</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Texto completo no recuperado</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: texto_no_recuperado</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Estudios</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: total</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>no_asignable_en_el_resumen</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>No asignable en el resumen</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: no_asignable_en_el_resumen</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>no_asignable_en_el_resumen_pct</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>No asignable en el resumen (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: no_asignable_en_el_resumen_pct</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>silencio_del_articulo_pct</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>No declarado en el texto completo (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: silencio_del_articulo_pct</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Generado el 2026-10-19</t>
         </is>
@@ -704,54 +722,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>declarado_texto_completo</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>declarado_no_clasificable</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>no_declarado_texto_completo</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>texto_no_recuperado</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
-        <is>
-          <t>no_asignable_en_el_resumen</t>
-        </is>
-      </c>
-      <c r="I1" s="8" t="inlineStr">
-        <is>
-          <t>no_asignable_en_el_resumen_pct</t>
-        </is>
-      </c>
-      <c r="J1" s="8" t="inlineStr">
-        <is>
-          <t>silencio_del_articulo_pct</t>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Nombre interno de la variable</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Declarado en el texto completo</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Declarado pero no clasificable</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>No declarado en el texto completo</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Texto completo no recuperado</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Estudios</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>No asignable en el resumen</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>No asignable en el resumen (%)</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>No declarado en el texto completo (%)</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
+++ b/verificables revisión sistemática/S22_completitud_resumen_frente_a_texto.xlsx
@@ -691,7 +691,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
